--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_yearly.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -916,101 +916,105 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.100240007027905</v>
+        <v>6.257280820784802</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.3774670338474645</v>
+        <v>-0.5526941387114122</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.08991080425787042</v>
+        <v>0.09884197058667837</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1643299012213698</v>
+        <v>0.1268275899297044</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9120988355580801</v>
+        <v>0.8848338540187447</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.08627628706692314</v>
+        <v>0.07350245796822708</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.3759620822245726</v>
+        <v>0.3938772377930511</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5269644188142332</v>
+        <v>0.5449626035199259</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.21463809261531</v>
+        <v>0.2409623232055411</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3663698603541443</v>
+        <v>0.5617214716190287</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>-0.203348204356904</v>
+        <v>-0.4275853055628839</v>
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1028,7 +1032,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1059,51 +1063,51 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>6.257280820784802</v>
+        <v>12.6233029259168</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.5526941387114122</v>
+        <v>-0.1603214207420498</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.4524433971482912</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.09884197058667837</v>
+        <v>0.1510583718736254</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1268275899297044</v>
+        <v>0.179953859103356</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8848338540187447</v>
+        <v>0.9223232036353308</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.07350245796822708</v>
+        <v>0.09797037712621459</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.3938772377930511</v>
+        <v>0.4028126637259931</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5449626035199259</v>
+        <v>0.5624301700995736</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0.2409623232055411</v>
+        <v>0.2165362070564247</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.5617214716190287</v>
+        <v>0.6736562835258951</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
@@ -1115,23 +1119,23 @@
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>-0.4275853055628839</v>
+        <v>0.0745317666678964</v>
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
@@ -1143,11 +1147,11 @@
         </is>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1165,7 +1169,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1183,61 +1187,57 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>12.6233029259168</v>
+        <v>7.715468189656733</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1603214207420498</v>
+        <v>-0.4628180855366</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4524433971482912</v>
+        <v>-0.5319062364980358</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1510583718736254</v>
+        <v>0.1887900651185331</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.179953859103356</v>
+        <v>0.175290390715004</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9223232036353308</v>
+        <v>0.9387957966486794</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.09797037712621459</v>
+        <v>0.08055922295419604</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.4028126637259931</v>
+        <v>0.3223335810362195</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5624301700995736</v>
+        <v>0.4498923746603672</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.2165362070564247</v>
+        <v>0.1514538041226624</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.6736562835258951</v>
+        <v>0.7548104302303326</v>
       </c>
       <c r="V6" s="2" t="n">
         <v>0.3333333333333333</v>
@@ -1248,27 +1248,25 @@
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.0745317666678964</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0.3488098219881399</v>
-      </c>
+        <v>-0.312571445992458</v>
+      </c>
+      <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="n">
         <v>0.5</v>
       </c>
@@ -1278,11 +1276,11 @@
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1293,30 +1291,12 @@
           <t>1/6</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AN6" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1326,7 +1306,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1357,51 +1337,51 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.715468189656733</v>
+        <v>10.14921981828208</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.4628180855366</v>
+        <v>-0.3128126778242608</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>-0.5319062364980358</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1887900651185331</v>
+        <v>0.2026301449129275</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.175290390715004</v>
+        <v>0.1918659215535435</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9387957966486794</v>
+        <v>0.9328315819369497</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.08055922295419604</v>
+        <v>0.09012411152434718</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.3223335810362195</v>
+        <v>0.3404213054891188</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.4498923746603672</v>
+        <v>0.4757284482325497</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>0.1514538041226624</v>
+        <v>0.1694360873031049</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.7548104302303326</v>
+        <v>0.7418894994411747</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
@@ -1413,39 +1393,39 @@
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>-0.312571445992458</v>
+        <v>-0.1206104031118328</v>
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1463,7 +1443,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1481,106 +1461,100 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.14921981828208</v>
+        <v>5.293531879009563</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3128126778242608</v>
+        <v>-0.6120952506584788</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.5319062364980358</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2026301449129275</v>
+        <v>0.1577599127604853</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1918659215535435</v>
+        <v>0.1414044586053625</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9328315819369497</v>
+        <v>0.8074410678784436</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.09012411152434718</v>
+        <v>0.06804282717371457</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.3404213054891188</v>
+        <v>0.3171666208888113</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.4757284482325497</v>
+        <v>0.4420848730965823</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0.1694360873031049</v>
+        <v>0.1462024820556934</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.7418894994411747</v>
+        <v>0.7271522785473131</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>-0.5036005610895</v>
+      </c>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="Z8" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.1206104031118328</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0.1038569192934302</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
       <c r="AF8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1591,30 +1565,12 @@
           <t>0/6</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AL8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AN8" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1624,7 +1580,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1655,51 +1611,51 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5.293531879009563</v>
+        <v>11.06502217468845</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.6120952506584788</v>
+        <v>-0.2563667758509962</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4654013134181593</v>
+        <v>-0.4944489880306537</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1577599127604853</v>
+        <v>0.1702165150870926</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1414044586053625</v>
+        <v>0.1825753561607068</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.8074410678784436</v>
+        <v>0.926583357000852</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.06804282717371457</v>
+        <v>0.09320798626829707</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.3171666208888113</v>
+        <v>0.3732135141607358</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.4420848730965823</v>
+        <v>0.5226573021725762</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>0.1462024820556934</v>
+        <v>0.1885088017664596</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.7271522785473131</v>
+        <v>0.7880224184927284</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
@@ -1711,39 +1667,39 @@
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>-0.5036005610895</v>
+        <v>-0.04837691250391973</v>
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="AF9" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
       <c r="AH9" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1752,167 +1708,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>11.06502217468845</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.2563667758509962</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.4944489880306537</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1702165150870926</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1825753561607068</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.926583357000852</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>0.09320798626829707</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.3732135141607358</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.5226573021725762</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>0.1885088017664596</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.7880224184927284</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.04837691250391973</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0.1945282652979952</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1925,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2310,7 +2105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2320,7 +2115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2331,68 +2126,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4355826533357545</v>
+        <v>0.03426375546556626</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.5835345717831015</v>
+        <v>0.1408555329895731</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.2320386692235181</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0881793893681919</v>
+        <v>0.1691479802421611</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1489104471765209</v>
+        <v>0.09634651057285501</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9462603878116344</v>
+        <v>0.9950138504155125</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1452528993287905</v>
+        <v>-0.175697623167833</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.6141277895968544</v>
+        <v>0.5566351408863635</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.3087473051992134</v>
+        <v>0.3734601369999864</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.2320386692235181</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.6795408281682738</v>
+        <v>0.2547140279278228</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.01895340505933174</v>
+        <v>-0.2671015172251868</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.9544262269956552</v>
+        <v>0.3577500255478659</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1145536846800933</v>
+        <v>-0.08137866847282127</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.6690509366290767</v>
+        <v>0.2024656927765038</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.6969679201140271</v>
+        <v>0.6365246385269754</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.01645109677917489</v>
+        <v>-0.2652321483782639</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2408,7 +2207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2439,62 +2238,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.03426375546556626</v>
+        <v>0.01949386164648326</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.1408555329895731</v>
+        <v>0.1245634459894014</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2320386692235181</v>
+        <v>-0.4430822889269981</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1691479802421611</v>
+        <v>0.2290395955711476</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.09634651057285501</v>
+        <v>0.1594314032930243</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9950138504155125</v>
+        <v>0.9977839335180055</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.175697623167833</v>
+        <v>-0.3860073924418943</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.5566351408863635</v>
+        <v>0.1594804237280474</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.3734601369999864</v>
+        <v>0.8204913137991163</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2320386692235181</v>
+        <v>-0.4430822889269981</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2547140279278228</v>
+        <v>0.6604334467496051</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2671015172251868</v>
+        <v>-0.03011433140576725</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3577500255478659</v>
+        <v>0.9275895967311513</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.08137866847282127</v>
+        <v>-0.1145536846800933</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.2024656927765038</v>
+        <v>0.1852937765128384</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.6365246385269754</v>
+        <v>0.2189871804128622</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2652321483782639</v>
+        <v>-0.02764049076267772</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2510,7 +2309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2528,89 +2327,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.01949386164648326</v>
+        <v>-0.1398808617338245</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1245634459894014</v>
+        <v>-0.05123652188751626</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4430822889269981</v>
+        <v>-0.5311044950287367</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2290395955711476</v>
+        <v>0.3244669395004775</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1594314032930243</v>
+        <v>0.1800318889201953</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9977839335180055</v>
+        <v>0.9988919667590028</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3860073924418943</v>
+        <v>-0.4963092168449624</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1594804237280474</v>
+        <v>-0.04881655659796225</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8204913137991163</v>
+        <v>1.05494715736832</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4430822889269981</v>
+        <v>-0.5311044950287367</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.6604334467496051</v>
+        <v>0.7076332683288911</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.03011433140576725</v>
+        <v>-0.002544162544396711</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9275895967311513</v>
+        <v>0.993882519477554</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1145536846800933</v>
+        <v>-0.1384848318129372</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1852937765128384</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2189871804128622</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.02764049076267772</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.289839662469059</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.2816675165368164</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.01137655072041766</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -2622,7 +2411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2653,7 +2442,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -2724,7 +2513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2742,40 +2531,36 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.1398808617338245</v>
+        <v>-0.1173837441188266</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.05123652188751626</v>
+        <v>-0.02642083926134298</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.3244669395004775</v>
+        <v>0.2797073958169614</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1800318889201953</v>
+        <v>0.145181942739044</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>0.9988919667590028</v>
@@ -2784,47 +2569,41 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4963092168449624</v>
+        <v>-0.4257304063203509</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.04881655659796225</v>
+        <v>0.08446639848314375</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.05494715736832</v>
+        <v>0.9049259346985113</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.7076332683288911</v>
+        <v>0.5369371208142575</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.002544162544396711</v>
+        <v>-0.1022505057783126</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.993882519477554</v>
+        <v>0.7541369835481917</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1384848318129372</v>
+        <v>-0.08137866847282105</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0</v>
+        <v>0.02615581564705982</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>0.1401232916801005</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.4008571110360091</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.4107136686869098</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.01672626213633355</v>
-      </c>
+        <v>-0.0999606593994733</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -2836,7 +2615,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2867,23 +2646,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.1173837441188266</v>
+        <v>-0.0512155174755996</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.02642083926134298</v>
+        <v>0.04656672031919462</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4654013134181593</v>
+        <v>-0.4858060135695987</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2797073958169614</v>
+        <v>0.2690579963856294</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.145181942739044</v>
+        <v>0.1670691382037733</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>0.9988919667590028</v>
@@ -2892,155 +2671,43 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.4257304063203509</v>
+        <v>-0.4476492758560092</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.08446639848314375</v>
+        <v>0.04307420609516011</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.9049259346985113</v>
+        <v>0.9515163431063268</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.4654013134181593</v>
+        <v>-0.4858060135695987</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.5369371208142575</v>
+        <v>0.7177210801973428</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1022505057783126</v>
+        <v>0.00334828931980713</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7541369835481917</v>
+        <v>1.008051016529013</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.08137866847282105</v>
+        <v>-0.1321147286483807</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.02615581564705982</v>
+        <v>0.1030849568548795</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1401232916801005</v>
+        <v>0.09660677267937134</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.0999606593994733</v>
+        <v>0.005907481457259056</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.0512155174755996</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.04656672031919462</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.4858060135695987</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.2690579963856294</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1670691382037733</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9988919667590028</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.4476492758560092</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.04307420609516011</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.9515163431063268</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.4858060135695987</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.7177210801973428</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.00334828931980713</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>1.008051016529013</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.1321147286483807</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.1030849568548795</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.09660677267937134</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>0.005907481457259056</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.3390944921772481</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.3537846180346855</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.02273255367701243</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3053,7 +2720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3438,7 +3105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3448,7 +3115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3459,68 +3126,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3499625568620768</v>
+        <v>-0.03588315428087374</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.2815106712242617</v>
+        <v>-0.08477015172327707</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1399665328165783</v>
+        <v>0.08522082414153055</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1982343541210623</v>
+        <v>0.04852502486469504</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.936046511627907</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.08701691433111236</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.2045306567846077</v>
+        <v>0.8388723071338657</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7983203326963466</v>
+        <v>0.1728208842981709</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.257317798460998</v>
+        <v>0.05600734652469064</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.0639087216303369</v>
+        <v>-0.5022874374005696</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.120882518504188</v>
+        <v>0.04992982339403304</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1172405796580748</v>
+        <v>-0.01333427532540465</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.125740496352519</v>
+        <v>-0.1960181629300093</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1690562117043539</v>
+        <v>0.7847159647430844</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.03705186706863761</v>
+        <v>-0.5495183250710001</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3536,7 +3207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3567,62 +3238,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.03588315428087374</v>
+        <v>0.219973425690712</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.08477015172327707</v>
+        <v>0.1581128348231637</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.08522082414153055</v>
+        <v>0.1716435077047097</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.04852502486469504</v>
+        <v>0.1999916015372289</v>
       </c>
       <c r="O5" s="2" t="n">
+        <v>0.9607558139534884</v>
+      </c>
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="P5" t="b">
-        <v>0</v>
-      </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.08701691433111236</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.8388723071338657</v>
+        <v>0.1367261802868205</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.1728208842981709</v>
+        <v>0.8651796704442967</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.05600734652469064</v>
+        <v>1.161639904847755</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.5022874374005696</v>
+        <v>0.01881425351789412</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.04992982339403304</v>
+        <v>1.035586916636739</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.01333427532540465</v>
+        <v>-0.1172405796580748</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1960181629300093</v>
+        <v>0.01734191277592623</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.7847159647430844</v>
+        <v>0.1032486343009715</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.5495183250710001</v>
+        <v>-0.07786705449173448</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -3638,7 +3309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3656,89 +3327,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.219973425690712</v>
+        <v>0.4587322504434632</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1581128348231637</v>
+        <v>0.3847650335929069</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1716435077047097</v>
+        <v>0.0697761368206746</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1999916015372289</v>
+        <v>0.144427223143356</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9607558139534884</v>
+        <v>0.9295058139534884</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.2869026592132758</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1367261802868205</v>
+        <v>0.4362751871824671</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8651796704442967</v>
+        <v>0.5698061308410138</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.161639904847755</v>
+        <v>1.045628509614295</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.01881425351789412</v>
+        <v>-0.03586370776940528</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.035586916636739</v>
+        <v>0.9321642616614942</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1172405796580748</v>
+        <v>-0.1220563520675992</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.01734191277592623</v>
+        <v>0.216444085291343</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1032486343009715</v>
+        <v>0.3939756699714687</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.07786705449173448</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.09629091600400996</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.05629120032427037</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.04238565508076653</v>
-      </c>
+        <v>-0.127356300762236</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -3750,7 +3411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3781,62 +3442,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4587322504434632</v>
+        <v>0.3039346135672543</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.3847650335929069</v>
+        <v>0.2378166441514451</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2869026592132757</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.0697761368206746</v>
+        <v>0.1630116906248304</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.144427223143356</v>
+        <v>0.2090293332448557</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9295058139534884</v>
+        <v>0.9491279069767442</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2869026592132758</v>
+        <v>-0.4425366612330849</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4362751871824671</v>
+        <v>0.1228071056210567</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5698061308410138</v>
+        <v>0.8789047246337144</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2869026592132757</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>1.045628509614295</v>
+        <v>1.339049983899392</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.03586370776940528</v>
+        <v>0.1024303622186051</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.9321642616614942</v>
+        <v>1.19374570231434</v>
       </c>
       <c r="X7" s="2" t="n">
         <v>-0.1220563520675992</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.216444085291343</v>
+        <v>0.08735756530942274</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.3939756699714687</v>
+        <v>0.08973948813890953</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.127356300762236</v>
+        <v>-0.002185772705690314</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3852,7 +3513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3870,89 +3531,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3039346135672543</v>
+        <v>0.3891351470281907</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.2378166441514451</v>
+        <v>0.3186969561787549</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4425366612330848</v>
+        <v>-0.1710251013839396</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1630116906248304</v>
+        <v>0.07443483028736213</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2090293332448557</v>
+        <v>0.1254223907378349</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9491279069767442</v>
+        <v>0.9338662790697675</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4425366612330849</v>
+        <v>-0.08701691433111214</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1228071056210567</v>
+        <v>0.8388723071338662</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8789047246337144</v>
+        <v>0.1728208842981705</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4425366612330848</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.339049983899392</v>
+        <v>0.5215343732359017</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.1024303622186051</v>
+        <v>-0.2828773639893871</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.19374570231434</v>
+        <v>0.4649411330013035</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1220563520675992</v>
+        <v>-0.1220563520675991</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.08735756530942274</v>
+        <v>0.1584067142952739</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.08973948813890953</v>
+        <v>0.7847159647430848</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.002185772705690314</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.03409571847815707</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.06784680049713732</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.03620765560530192</v>
-      </c>
+        <v>-0.3509293707348946</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -3964,7 +3615,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3995,180 +3646,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3891351470281907</v>
+        <v>0.2844762390765461</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.3186969561787549</v>
+        <v>0.2193449358601549</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1710251013839396</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.07443483028736213</v>
+        <v>0.1679147172827054</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1254223907378349</v>
+        <v>0.2069922632706336</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9338662790697675</v>
+        <v>0.9498546511627907</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.08701691433111214</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.8388723071338662</v>
+        <v>0.1367261802868205</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1728208842981705</v>
+        <v>0.8651796704442967</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.5215343732359017</v>
+        <v>1.275930800414455</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2828773639893871</v>
+        <v>0.0726813167551823</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.4649411330013035</v>
+        <v>1.137475768462195</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1220563520675991</v>
+        <v>-0.1220563520675992</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1584067142952739</v>
+        <v>0.07113112995680071</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.7847159647430848</v>
+        <v>0.1032486343009715</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.3509293707348946</v>
+        <v>-0.0291117553610396</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.2844762390765461</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.2193449358601549</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.435625969452745</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1679147172827054</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2069922632706336</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9498546511627907</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.435625969452745</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1367261802868205</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.8651796704442967</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.435625969452745</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>1.275930800414455</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.0726813167551823</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>1.137475768462195</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.1220563520675992</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.07113112995680071</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.1032486343009715</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.0291117553610396</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.04850972899407713</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.05629120032427037</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.008245627605535821</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4181,7 +3720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4566,7 +4105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4576,7 +4115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4587,68 +4126,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.004205705299217932</v>
+        <v>0.007859810079829055</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.01876488188421255</v>
+        <v>-0.01519436250049522</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04678097528829382</v>
+        <v>0.07584506561778712</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1552469470901619</v>
+        <v>0.2200814955608066</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9793103448275862</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.138687252248779</v>
+        <v>-0.191725710108013</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07053469759807562</v>
+        <v>0.004612638980404427</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7096268615961698</v>
+        <v>0.9810109562715352</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1659013615217844</v>
+        <v>0.2469279583475474</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08341586655962385</v>
+        <v>-0.01971605842128576</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.6099159566998359</v>
+        <v>0.9078002770441747</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02192041710993009</v>
+        <v>-0.03283823265868402</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.003625608188822849</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.06561938010711899</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.06498097687467108</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4664,7 +4207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4695,23 +4238,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.007859810079829055</v>
+        <v>0.007859810079828833</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.01519436250049522</v>
+        <v>-0.01519436250049544</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>-0.1941024876751378</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.07584506561778712</v>
+        <v>0.07584506561778721</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2200814955608066</v>
+        <v>0.2200814955608064</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>0.9793103448275862</v>
@@ -4732,25 +4275,25 @@
         <v>-0.1941024876751378</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2469279583475474</v>
+        <v>0.2469279583475472</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.01971605842128576</v>
+        <v>-0.01971605842128599</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9078002770441747</v>
+        <v>0.9078002770441739</v>
       </c>
       <c r="X5" s="2" t="n">
         <v>-0.03283823265868402</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -4766,7 +4309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4784,89 +4327,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.007859810079828833</v>
+        <v>-0.12013798743183</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.01519436250049544</v>
+        <v>-0.1402642892068867</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1941024876751377</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.07584506561778721</v>
+        <v>0.1069807703566161</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2200814955608064</v>
+        <v>0.193060997030619</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9862068965517241</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.1917257101080129</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.004612638980404427</v>
+        <v>0.004612638980404649</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.9810109562715352</v>
+        <v>0.9810109562715347</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1941024876751377</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2469279583475472</v>
+        <v>0.08856860050039383</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.01971605842128599</v>
+        <v>-0.1442117315329907</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9078002770441739</v>
+        <v>0.3256115695028219</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.03283823265868402</v>
+        <v>-0.0004382006475144307</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1269996047382033</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0.003638801055728003</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.06157862866619668</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.06949695703245728</v>
-      </c>
+        <v>-0.1269996047382034</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -4878,7 +4411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4909,23 +4442,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.12013798743183</v>
+        <v>-0.0453726834078465</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1402642892068867</v>
+        <v>-0.06720919547678605</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1941024876751377</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1069807703566161</v>
+        <v>0.08400699976983923</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.193060997030619</v>
+        <v>0.2070697545900752</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0.9862068965517241</v>
@@ -4934,37 +4467,37 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1917257101080129</v>
+        <v>-0.191725710108013</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.004612638980404649</v>
+        <v>0.004612638980404427</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.9810109562715347</v>
+        <v>0.9810109562715352</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1941024876751377</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.08856860050039383</v>
+        <v>0.1810685166290817</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1442117315329907</v>
+        <v>-0.07149206736049396</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3256115695028219</v>
+        <v>0.6656761375255211</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.0004382006475144307</v>
+        <v>-0.02015338344400641</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.1269996047382033</v>
+        <v>-0.0528173590764166</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1269996047382034</v>
+        <v>-0.0528173590764166</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4980,7 +4513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4998,40 +4531,36 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.0453726834078465</v>
+        <v>-0.1201379874318304</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.06720919547678605</v>
+        <v>-0.140264289206887</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1941024876751383</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.08400699976983923</v>
+        <v>0.1069807703566164</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2070697545900752</v>
+        <v>0.1930609970306191</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>0.9862068965517241</v>
@@ -5040,47 +4569,41 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.1917257101080133</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.004612638980404427</v>
+        <v>0.004612638980403982</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9810109562715352</v>
+        <v>0.981010956271537</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1941024876751383</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1810685166290817</v>
+        <v>0.08856860050039406</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.07149206736049396</v>
+        <v>-0.1442117315329905</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6656761375255211</v>
+        <v>0.3256115695028227</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02015338344400641</v>
+        <v>-0.0004382006475144307</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.0528173590764166</v>
+        <v>-0.1269996047382036</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.0528173590764166</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.04937074988265655</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.06157862866619668</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.01300895222173892</v>
-      </c>
+        <v>-0.1269996047382032</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -5092,7 +4615,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5123,23 +4646,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.1201379874318304</v>
+        <v>-0.0453726834078465</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.140264289206887</v>
+        <v>-0.06720919547678605</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1941024876751383</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1069807703566164</v>
+        <v>0.08400699976983923</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1930609970306191</v>
+        <v>0.2070697545900752</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>0.9862068965517241</v>
@@ -5148,155 +4671,43 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1917257101080133</v>
+        <v>-0.191725710108013</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.004612638980403982</v>
+        <v>0.004612638980404427</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.981010956271537</v>
+        <v>0.9810109562715352</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1941024876751383</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.08856860050039406</v>
+        <v>0.1810685166290817</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1442117315329905</v>
+        <v>-0.07149206736049396</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3256115695028227</v>
+        <v>0.6656761375255211</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0004382006475144307</v>
+        <v>-0.02015338344400641</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1269996047382036</v>
+        <v>-0.0528173590764166</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1269996047382032</v>
+        <v>-0.0528173590764166</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.0453726834078465</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.06720919547678605</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.1941024876751378</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.08400699976983923</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2070697545900752</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9862068965517241</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.191725710108013</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.004612638980404427</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.9810109562715352</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.1941024876751378</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.1810685166290817</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.07149206736049396</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.6656761375255211</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.02015338344400641</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.0528173590764166</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.0528173590764166</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.04937074988265655</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.06157862866619668</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.01300895222173892</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5309,7 +4720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5694,7 +5105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5704,7 +5115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5715,68 +5126,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.001560322013030691</v>
+        <v>0.06404560575472318</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08768794751503295</v>
+        <v>-0.0307706793210285</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1125125693043114</v>
+        <v>0.1160654159706604</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4092856064157859</v>
+        <v>0.4686838807519483</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9098360655737705</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.007998764021966531</v>
+        <v>-0.02087621099141768</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9804376909420194</v>
+        <v>1.051056249472068</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3998874441902356</v>
+        <v>0.5310826913419406</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09492740958848467</v>
+        <v>-0.01010543144869325</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7314395722407911</v>
+        <v>0.9714105862119551</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.08260648781657542</v>
+        <v>-0.06450069847101803</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.05872425336259124</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.02949062757694998</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.08568789125080933</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5792,7 +5207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5823,23 +5238,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.06404560575472318</v>
+        <v>0.06404560575472296</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.0307706793210285</v>
+        <v>-0.03077067932102873</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>-0.3050371402068923</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1160654159706604</v>
+        <v>0.1160654159706605</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4686838807519483</v>
+        <v>0.4686838807519479</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>0.9098360655737705</v>
@@ -5860,25 +5275,25 @@
         <v>-0.3050371402068923</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.5310826913419406</v>
+        <v>0.5310826913419402</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.01010543144869325</v>
+        <v>-0.01010543144869347</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9714105862119551</v>
+        <v>0.9714105862119542</v>
       </c>
       <c r="X5" s="2" t="n">
         <v>-0.06450069847101803</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5894,7 +5309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5912,40 +5327,36 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.06404560575472296</v>
+        <v>0.06404560575472318</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.03077067932102873</v>
+        <v>-0.0307706793210285</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>-0.3050371402068923</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1160654159706605</v>
+        <v>0.1160654159706604</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4686838807519479</v>
+        <v>0.4686838807519481</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>0.9098360655737705</v>
@@ -5966,35 +5377,29 @@
         <v>-0.3050371402068923</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.5310826913419402</v>
+        <v>0.5310826913419404</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.01010543144869347</v>
+        <v>-0.01010543144869336</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9714105862119542</v>
+        <v>0.9714105862119546</v>
       </c>
       <c r="X6" s="2" t="n">
         <v>-0.06450069847101803</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0.0623879384679531</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.0286458436696605</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.09371842550355503</v>
-      </c>
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -6006,7 +5411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6037,23 +5442,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.06404560575472318</v>
+        <v>0.06404560575472296</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.0307706793210285</v>
+        <v>-0.03077067932102873</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>-0.3050371402068923</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1160654159706604</v>
+        <v>0.1160654159706605</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4686838807519481</v>
+        <v>0.4686838807519479</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0.9098360655737705</v>
@@ -6074,25 +5479,25 @@
         <v>-0.3050371402068923</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5310826913419404</v>
+        <v>0.5310826913419402</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.01010543144869336</v>
+        <v>-0.01010543144869347</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.9714105862119546</v>
+        <v>0.9714105862119542</v>
       </c>
       <c r="X7" s="2" t="n">
         <v>-0.06450069847101803</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6108,7 +5513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6126,40 +5531,36 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.06404560575472296</v>
+        <v>0.06404560575472207</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.03077067932102873</v>
+        <v>-0.03077067932102961</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1160654159706605</v>
+        <v>0.1160654159706604</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4686838807519479</v>
+        <v>0.4686838807519478</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>0.9098360655737705</v>
@@ -6168,47 +5569,41 @@
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02087621099141768</v>
+        <v>-0.02087621099141745</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.051056249472068</v>
+        <v>1.051056249472067</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.5310826913419402</v>
+        <v>0.5310826913419389</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.01010543144869347</v>
+        <v>-0.01010543144869436</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.9714105862119542</v>
+        <v>0.9714105862119518</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.06450069847101803</v>
+        <v>-0.0645006984710178</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.0623879384679531</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.0286458436696605</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.09371842550355503</v>
-      </c>
+        <v>-8.881784197001252e-16</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -6220,7 +5615,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6251,23 +5646,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.06404560575472207</v>
+        <v>0.06404560575472296</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.03077067932102961</v>
+        <v>-0.03077067932102873</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1160654159706604</v>
+        <v>0.1160654159706605</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4686838807519478</v>
+        <v>0.4686838807519479</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>0.9098360655737705</v>
@@ -6276,155 +5671,43 @@
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.02087621099141745</v>
+        <v>-0.02087621099141768</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.051056249472067</v>
+        <v>1.051056249472068</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.5310826913419389</v>
+        <v>0.5310826913419402</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.01010543144869436</v>
+        <v>-0.01010543144869347</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.9714105862119518</v>
+        <v>0.9714105862119542</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0645006984710178</v>
+        <v>-0.06450069847101803</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.06404560575472296</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.03077067932102873</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1160654159706605</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.4686838807519479</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9098360655737705</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>-0.02087621099141768</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>1.051056249472068</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.5310826913419402</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.01010543144869347</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.9714105862119542</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.06450069847101803</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.0623879384679531</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.0286458436696605</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.09371842550355503</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6437,7 +5720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6822,7 +6105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6832,7 +6115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6843,74 +6126,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.01404474995820859</v>
+        <v>0.123185785230272</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.04427100028277864</v>
+        <v>0.05859354536273642</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1240394247573673</v>
+        <v>0.0006360007504951526</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1633727596186971</v>
+        <v>0.02018470284987558</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9902534113060428</v>
+        <v>0.009746588693957114</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1179533974995302</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7372514143129777</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3142505667229638</v>
+        <v>0.1106314540976914</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1451083722677065</v>
+        <v>-0.2775582102492622</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.5848371626159791</v>
+        <v>0.2058910708906152</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.08922573857760219</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.09737419538112158</v>
+        <v>0.2154839294630535</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.07307531657611488</v>
+        <v>0.4064778166545429</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.02264415034961154</v>
+        <v>-0.1357958760030704</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.3125812952861471</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.2377963300225924</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6920,7 +6211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6951,62 +6242,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.123185785230272</v>
+        <v>0.04318694445603577</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.05859354536273642</v>
+        <v>-0.0168047169672535</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.00942253736259735</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0006360007504951526</v>
+        <v>0.1240441358056347</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.02018470284987558</v>
+        <v>0.1643136203906092</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.009746588693957114</v>
+        <v>0.9805068226120858</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>0.1179533974995302</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>0.7372514143129777</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1106314540976914</v>
+        <v>0.3520202466467532</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2775582102492622</v>
+        <v>-0.1205400106732447</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.2058910708906152</v>
+        <v>0.6551285631053725</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.00942253736259735</v>
+        <v>-0.08922573857760219</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.2154839294630535</v>
+        <v>0.1289111588534055</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.4064778166545429</v>
+        <v>0.07307531657611488</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1357958760030704</v>
+        <v>0.05203347930455382</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -7015,7 +6306,7 @@
         <v>0.3125812952861471</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.2377963300225924</v>
+        <v>-0.08318174614964868</v>
       </c>
     </row>
     <row r="6">
@@ -7026,7 +6317,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7044,95 +6335,81 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.04318694445603577</v>
+        <v>-0.1847525839528147</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.0168047169672535</v>
+        <v>-0.2316358844193643</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2830886953761897</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1240441358056347</v>
+        <v>0.2146905675263885</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1643136203906092</v>
+        <v>0.1799452418984483</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9805068226120858</v>
+        <v>1</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2809671323736413</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1179533974995302</v>
+        <v>0.04182193013870528</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7372514143129777</v>
+        <v>0.9068390294167656</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2809671323736413</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.3520202466467532</v>
+        <v>0.1338110575368356</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1205400106732447</v>
+        <v>-0.2624803785054345</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.6551285631053725</v>
+        <v>0.2490295563586896</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.08922573857760219</v>
+        <v>-0.08538770826029607</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1289111588534055</v>
+        <v>-0.117759371804658</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.07307531657611488</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.05203347930455382</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0.02873856848923895</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.02873856848923939</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.3125812952861471</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.08318174614964868</v>
-      </c>
+        <v>-0.117759371804658</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7142,7 +6419,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7173,23 +6450,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.1847525839528147</v>
+        <v>-0.07593530609125765</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.2316358844193643</v>
+        <v>-0.1290764775225159</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2830886953761897</v>
+        <v>-0.298221368786892</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2146905675263885</v>
+        <v>0.1908003349426301</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1799452418984483</v>
+        <v>0.1967758842540266</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
@@ -7207,28 +6484,28 @@
         <v>0.9068390294167656</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2809671323736413</v>
+        <v>-0.2809671323736415</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1338110575368356</v>
+        <v>0.2851494493697155</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2624803785054345</v>
+        <v>-0.164038021006592</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2490295563586896</v>
+        <v>0.530678422094654</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.08538770826029607</v>
+        <v>-0.1279869945573349</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.117759371804658</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.117759371804658</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7244,7 +6521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7262,89 +6539,79 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.07593530609125765</v>
+        <v>0.123185785230272</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1290764775225159</v>
+        <v>0.05859354536273642</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.298221368786892</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1908003349426301</v>
+        <v>0.0006360007504951526</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1967758842540266</v>
+        <v>0.0201847028498755</v>
       </c>
       <c r="O8" s="2" t="n">
+        <v>0.009746588693957114</v>
+      </c>
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2809671323736413</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.04182193013870528</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9068390294167656</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2809671323736415</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2851494493697155</v>
+        <v>0.1106314540976916</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.164038021006592</v>
+        <v>-0.2775582102492621</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.530678422094654</v>
+        <v>0.2058910708906156</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1279869945573349</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0</v>
+        <v>0.2154839294630535</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>0.4064778166545429</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.08873381184920537</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.06809896327620113</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>-0.0221427466649764</v>
-      </c>
+        <v>-0.1357958760030703</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -7356,7 +6623,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7387,180 +6654,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.123185785230272</v>
+        <v>0.04318694445603577</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.05859354536273642</v>
+        <v>-0.0168047169672535</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.00942253736259735</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.0006360007504951526</v>
+        <v>0.1240441358056347</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0201847028498755</v>
+        <v>0.1643136203906092</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.009746588693957114</v>
+        <v>0.9805068226120858</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>0.1179533974995302</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>0.7372514143129777</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1106314540976916</v>
+        <v>0.3520202466467532</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2775582102492621</v>
+        <v>-0.1205400106732447</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2058910708906156</v>
+        <v>0.6551285631053725</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.00942253736259735</v>
+        <v>-0.08922573857760219</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.2154839294630535</v>
+        <v>0.1289111588534055</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.4064778166545429</v>
+        <v>0.07307531657611488</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1357958760030703</v>
+        <v>0.05203347930455382</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.04318694445603577</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.0168047169672535</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1240441358056347</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1643136203906092</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9805068226120858</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1179533974995302</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7372514143129777</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.3520202466467532</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1205400106732447</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.6551285631053725</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.08922573857760219</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.1289111588534055</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.07307531657611488</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>0.05203347930455382</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.02873856848923895</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.02873856848923939</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7573,7 +6728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7958,7 +7113,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7968,7 +7123,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7979,74 +7134,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>0.01733422320252154</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.2152266720452526</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.03198399714010958</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.0622105130556192</v>
+        <v>0.01191759412390914</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.109227416058032</v>
+        <v>0.2750259996931479</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1545561592075562</v>
+        <v>-0.2063553257992853</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.03928937419683753</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8056,7 +7219,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8087,62 +7250,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.05944967618015007</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>-0.05719067958884594</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.0679413098331703</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2181663348217244</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1277711346285673</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5578762400716401</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.07500868839622021</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.1640065156290161</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2623547528124305</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.04964464462786422</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.01191759412390914</v>
+        <v>-0.0622105130556192</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2750259996931479</v>
+        <v>0.109227416058032</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2063553257992853</v>
+        <v>-0.1545561592075562</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -8151,7 +7314,7 @@
         <v>0.04615004380353627</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.03928937419683753</v>
+        <v>0.0214285775248475</v>
       </c>
     </row>
     <row r="6">
@@ -8162,7 +7325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8180,94 +7343,84 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>0.01733422320252154</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.2152266720452526</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.03198399714010958</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.0622105130556192</v>
+        <v>0.01191759412390914</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.109227416058032</v>
+        <v>0.2750259996931479</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1545561592075562</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.2063553257992853</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="n">
         <v>0.04615004380353627</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.0214285775248475</v>
+        <v>-0.03928937419683753</v>
       </c>
     </row>
     <row r="7">
@@ -8278,7 +7431,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8309,62 +7462,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.05944967618015007</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>-0.05719067958884594</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>0.0679413098331703</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2181663348217244</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1277711346285673</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5578762400716401</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.07500868839622021</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.1640065156290161</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2623547528124305</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.04964464462786422</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.01191759412390914</v>
+        <v>-0.0622105130556192</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.2750259996931479</v>
+        <v>0.109227416058032</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2063553257992853</v>
+        <v>-0.1545561592075562</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -8373,7 +7526,7 @@
         <v>0.04615004380353627</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.03928937419683753</v>
+        <v>0.0214285775248475</v>
       </c>
     </row>
     <row r="8">
@@ -8384,7 +7537,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8402,94 +7555,84 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>0.01733422320252154</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.2152266720452526</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.03198399714010958</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.0622105130556192</v>
+        <v>0.01191759412390914</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.109227416058032</v>
+        <v>0.2750259996931479</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1545561592075562</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.2063553257992853</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
         <v>0.04615004380353627</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.0214285775248475</v>
+        <v>-0.03928937419683753</v>
       </c>
     </row>
     <row r="9">
@@ -8500,7 +7643,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8531,62 +7674,62 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.05944967618015007</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>-0.05719067958884594</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>0.0679413098331703</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2181663348217244</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1277711346285673</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5578762400716401</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.07500868839622021</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.1640065156290161</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2623547528124305</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.04964464462786422</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.01191759412390914</v>
+        <v>-0.0622105130556192</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.2750259996931479</v>
+        <v>0.109227416058032</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2063553257992853</v>
+        <v>-0.1545561592075562</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -8595,122 +7738,6 @@
         <v>0.04615004380353627</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.03928937419683753</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.05944967618015007</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.05719067958884594</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.0679413098331703</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2181663348217244</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1277711346285673</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.5578762400716401</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.07500868839622021</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1640065156290161</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.2623547528124305</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.04964464462786422</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.0622105130556192</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.109227416058032</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.1545561592075562</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.04615004380353627</v>
-      </c>
-      <c r="AF10" s="2" t="n">
         <v>0.0214285775248475</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_mvo_yearly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>0.6541746872192167</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -966,27 +967,27 @@
         <v>0.5617214716190287</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -994,27 +995,27 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1103,27 +1104,27 @@
         <v>0.6736562835258951</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1131,27 +1132,27 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1240,27 +1241,27 @@
         <v>0.7548104302303326</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1268,27 +1269,27 @@
       </c>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr"/>
@@ -1377,27 +1378,27 @@
         <v>0.7418894994411747</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1405,19 +1406,19 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
@@ -1425,7 +1426,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1514,19 +1515,19 @@
         <v>0.7271522785473131</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
@@ -1534,7 +1535,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1542,19 +1543,19 @@
       </c>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1562,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr"/>
@@ -1651,27 +1652,27 @@
         <v>0.7880224184927284</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1679,27 +1680,27 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1950,28 +1951,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196766684</v>
+        <v>0.05644008609220896</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208207</v>
+        <v>0.08831268540851259</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571159</v>
+        <v>0.2970580221997939</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798217</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -1980,10 +1981,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278889</v>
+        <v>0.2724034021441999</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -1992,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1395291740668931</v>
+        <v>-0.08310591627223018</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2038,49 +2039,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.1398808617338245</v>
+        <v>0.05490478870196891</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.05123652188751626</v>
+        <v>-0.001453274454890408</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.3244669395004775</v>
+        <v>0.09909320577935192</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1800318889201953</v>
+        <v>0.3278361807192359</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.4963092168449624</v>
+        <v>-0.1795337383472572</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.04881655659796225</v>
+        <v>-0.01180949453260038</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.05494715736832</v>
+        <v>1.057769178806841</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1822864687558077</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.7076332683288911</v>
+        <v>0.2857381686566542</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.002544162544396711</v>
+        <v>0.0104799833841871</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.993882519477554</v>
+        <v>1.048952275953571</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1384848318129372</v>
+        <v>-0.1183724319722919</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2140,58 +2141,58 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.03426375546556626</v>
+        <v>0.05490478870196891</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.1408555329895731</v>
+        <v>-0.001453274454890408</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2320386692235181</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1691479802421611</v>
+        <v>0.09909320577935192</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.09634651057285501</v>
+        <v>0.3278361807192359</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9950138504155125</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.175697623167833</v>
+        <v>-0.1795337383472572</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.5566351408863635</v>
+        <v>-0.01180949453260038</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.3734601369999864</v>
+        <v>1.057769178806841</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2320386692235181</v>
+        <v>-0.1822864687558077</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2547140279278228</v>
+        <v>0.2857381686566542</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2671015172251868</v>
+        <v>0.0104799833841871</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.3577500255478659</v>
+        <v>1.048952275953571</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.08137866847282127</v>
+        <v>-0.1183724319722919</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.2024656927765038</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.6365246385269754</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2652321483782639</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2242,58 +2243,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.01949386164648326</v>
+        <v>0.05490478870196891</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.1245634459894014</v>
+        <v>-0.001453274454890408</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.4430822889269981</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2290395955711476</v>
+        <v>0.09909320577935192</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1594314032930243</v>
+        <v>0.3278361807192359</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9977839335180055</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3860073924418943</v>
+        <v>-0.1795337383472572</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1594804237280474</v>
+        <v>-0.01180949453260038</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.8204913137991163</v>
+        <v>1.057769178806841</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.4430822889269981</v>
+        <v>-0.1822864687558077</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.6604334467496051</v>
+        <v>0.2857381686566542</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.03011433140576725</v>
+        <v>0.0104799833841871</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9275895967311513</v>
+        <v>1.048952275953571</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1145536846800933</v>
+        <v>-0.1183724319722919</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.1852937765128384</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2189871804128622</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.02764049076267772</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2344,49 +2345,49 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.1398808617338245</v>
+        <v>0.05490478870196891</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.05123652188751626</v>
+        <v>-0.001453274454890408</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.3244669395004775</v>
+        <v>0.09909320577935192</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1800318889201953</v>
+        <v>0.3278361807192359</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4963092168449624</v>
+        <v>-0.1795337383472572</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.04881655659796225</v>
+        <v>-0.01180949453260038</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.05494715736832</v>
+        <v>1.057769178806841</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1822864687558077</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.7076332683288911</v>
+        <v>0.2857381686566542</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.002544162544396711</v>
+        <v>0.0104799833841871</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.993882519477554</v>
+        <v>1.048952275953571</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1384848318129372</v>
+        <v>-0.1183724319722919</v>
       </c>
       <c r="Y6" s="2" t="n">
         <v>0</v>
@@ -2446,49 +2447,49 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.1398808617338245</v>
+        <v>0.05490478870196891</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.05123652188751626</v>
+        <v>-0.001453274454890408</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.3244669395004775</v>
+        <v>0.09909320577935192</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1800318889201953</v>
+        <v>0.3278361807192359</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.4963092168449624</v>
+        <v>-0.1795337383472572</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.04881655659796225</v>
+        <v>-0.01180949453260038</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.05494715736832</v>
+        <v>1.057769178806841</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1822864687558077</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.7076332683288911</v>
+        <v>0.2857381686566542</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.002544162544396711</v>
+        <v>0.0104799833841871</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.993882519477554</v>
+        <v>1.048952275953571</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1384848318129372</v>
+        <v>-0.1183724319722919</v>
       </c>
       <c r="Y7" s="2" t="n">
         <v>0</v>
@@ -2548,64 +2549,68 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.1173837441188266</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.02642083926134298</v>
+        <v>-0.03796582501302292</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4654013134181593</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2797073958169614</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.145181942739044</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4257304063203509</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.08446639848314375</v>
+        <v>0.2117597153840098</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9049259346985113</v>
+        <v>-0.03587709265072057</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4654013134181593</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.5369371208142575</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1022505057783126</v>
+        <v>-0.2060850325577082</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7541369835481917</v>
+        <v>0.03737143334716829</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.08137866847282105</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.02615581564705982</v>
+        <v>-0.03656569054212289</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1401232916801005</v>
+        <v>0.2262410017903027</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.0999606593994733</v>
+        <v>-0.2143189568353445</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.3106955008082057</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.2164333699121769</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2650,64 +2655,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.0512155174755996</v>
+        <v>0.05457530154480694</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.04656672031919462</v>
+        <v>-0.001765158831013247</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4858060135695987</v>
+        <v>-0.1638829728650905</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2690579963856294</v>
+        <v>0.08632807107018847</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1670691382037733</v>
+        <v>0.2743481803517016</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.4476492758560092</v>
+        <v>-0.1638829728650905</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.04307420609516011</v>
+        <v>0.007040686852822553</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.9515163431063268</v>
+        <v>0.9655586700513826</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.4858060135695987</v>
+        <v>-0.1638829728650905</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.7177210801973428</v>
+        <v>0.2612771505903666</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.00334828931980713</v>
+        <v>-0.008744279946975797</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1.008051016529013</v>
+        <v>0.959155240109874</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1321147286483807</v>
+        <v>-0.04301643911502739</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1030849568548795</v>
+        <v>-0.000312338289380043</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.09660677267937134</v>
+        <v>0.01907545284146095</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.005907481457259056</v>
+        <v>-0.01902488287474935</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.3106955008082057</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.05120697764807369</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2950,28 +2959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.0534149946425504</v>
+        <v>-0.09123360655355228</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2216991067360385</v>
+        <v>0.2716992530341478</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389480542019929</v>
+        <v>0.1810585772249195</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.5035092528573141</v>
+        <v>-0.4707583434268607</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2980,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.121721302370637</v>
+        <v>0.717110477150922</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2992,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756414</v>
+        <v>-0.1395291740668931</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3038,49 +3047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1991773958883538</v>
+        <v>-0.1430381740072413</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.1383712990484478</v>
+        <v>-0.057005373248039</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4884434813691406</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2057028412243141</v>
+        <v>0.3246257835002017</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2187686648988483</v>
+        <v>0.1801113732573058</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9636627906976745</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.4884434813691407</v>
+        <v>-0.4996173751341991</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.03034451613625655</v>
+        <v>-0.05452902534959503</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9700784615125182</v>
+        <v>1.061303282480902</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4884434813691406</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.344173815041704</v>
+        <v>0.7126130752893149</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1048453029257503</v>
+        <v>-0.002619168609971578</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.198313531356619</v>
+        <v>0.9937284393340964</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1220563520675992</v>
+        <v>-0.1384848318129372</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3140,58 +3149,58 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.03588315428087374</v>
+        <v>0.03046719577540058</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08477015172327707</v>
+        <v>0.1339186871418176</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.232038669223518</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.08522082414153055</v>
+        <v>0.1692417031613319</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.04852502486469504</v>
+        <v>0.0963624029601982</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9955629506378258</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.08701691433111236</v>
+        <v>-0.1811115057163162</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.8388723071338657</v>
+        <v>0.5472865450275008</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.1728208842981709</v>
+        <v>0.3847228801043109</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.232038669223518</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.05600734652469064</v>
+        <v>0.2583730299896243</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.5022874374005696</v>
+        <v>-0.2671566292708479</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.04992982339403304</v>
+        <v>0.3602973854407199</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.01333427532540465</v>
+        <v>-0.08137866847282127</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.1960181629300093</v>
+        <v>0.2024656927765041</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.7847159647430844</v>
+        <v>0.6365246385269752</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.5495183250710001</v>
+        <v>-0.265232148378264</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3242,58 +3251,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.219973425690712</v>
+        <v>0.01575151905829486</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.1581128348231637</v>
+        <v>0.1177256623741463</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.4430822889269979</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1716435077047097</v>
+        <v>0.2291665122577949</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1999916015372289</v>
+        <v>0.159497133210856</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9607558139534884</v>
+        <v>0.9983361064891847</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.3900399949872505</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1367261802868205</v>
+        <v>0.1525169975512977</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.8651796704442967</v>
+        <v>0.8285354905193496</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.4430822889269979</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1.161639904847755</v>
+        <v>0.6652756094017394</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.01881425351789412</v>
+        <v>-0.03018726426687968</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.035586916636739</v>
+        <v>0.9277170402597903</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1172405796580748</v>
+        <v>-0.1145536846800933</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.01734191277592623</v>
+        <v>0.1852937765128384</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1032486343009715</v>
+        <v>0.218987180412862</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.07786705449173448</v>
+        <v>-0.02764049076267783</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -3344,58 +3353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.4587322504434632</v>
+        <v>-0.1430381740072413</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.3847650335929069</v>
+        <v>-0.057005373248039</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2869026592132757</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.0697761368206746</v>
+        <v>0.3246257835002017</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.144427223143356</v>
+        <v>0.1801113732573058</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9295058139534884</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2869026592132758</v>
+        <v>-0.4996173751341991</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.4362751871824671</v>
+        <v>-0.05452902534959503</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5698061308410138</v>
+        <v>1.061303282480902</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2869026592132757</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.045628509614295</v>
+        <v>0.7126130752893149</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.03586370776940528</v>
+        <v>-0.002619168609971578</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9321642616614942</v>
+        <v>0.9937284393340964</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1220563520675992</v>
+        <v>-0.1384848318129372</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.216444085291343</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.3939756699714687</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.127356300762236</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -3446,58 +3455,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3039346135672543</v>
+        <v>-0.1430381740072413</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.2378166441514451</v>
+        <v>-0.057005373248039</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.4425366612330848</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1630116906248304</v>
+        <v>0.3246257835002017</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2090293332448557</v>
+        <v>0.1801113732573058</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9491279069767442</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.4425366612330849</v>
+        <v>-0.4996173751341991</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1228071056210567</v>
+        <v>-0.05452902534959503</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.8789047246337144</v>
+        <v>1.061303282480902</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.4425366612330848</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>1.339049983899392</v>
+        <v>0.7126130752893149</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.1024303622186051</v>
+        <v>-0.002619168609971578</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.19374570231434</v>
+        <v>0.9937284393340964</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1220563520675992</v>
+        <v>-0.1384848318129372</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.08735756530942274</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.08973948813890953</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.002185772705690314</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3548,58 +3557,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3891351470281907</v>
+        <v>-0.1206236384700066</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.3186969561787549</v>
+        <v>-0.03234057963454628</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1710251013839396</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07443483028736213</v>
+        <v>0.2798444450564124</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1254223907378349</v>
+        <v>0.1452372492878466</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9338662790697675</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.08701691433111214</v>
+        <v>-0.429502114638474</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.8388723071338662</v>
+        <v>0.07795347980641298</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.1728208842981705</v>
+        <v>0.912362193120011</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1193545340586639</v>
+        <v>-0.4654013134181593</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.5215343732359017</v>
+        <v>0.5414191429872353</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.2828773639893871</v>
+        <v>-0.1023180141881137</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.4649411330013035</v>
+        <v>0.7550010217927536</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1220563520675991</v>
+        <v>-0.08137866847282105</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1584067142952739</v>
+        <v>0.02615581564706027</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.7847159647430848</v>
+        <v>0.140123291680101</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.3509293707348946</v>
+        <v>-0.0999606593994733</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -3650,58 +3659,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.2844762390765461</v>
+        <v>-0.05469830114849894</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.2193449358601549</v>
+        <v>0.0402031871650701</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.4858060135695986</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1679147172827054</v>
+        <v>0.2692020876672501</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2069922632706336</v>
+        <v>0.1671400209561885</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9498546511627907</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.4512770246410817</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1367261802868205</v>
+        <v>0.03680987417339998</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.8651796704442967</v>
+        <v>0.9586171566414186</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.435625969452745</v>
+        <v>-0.4858060135695986</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>1.275930800414455</v>
+        <v>0.7227303052750462</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.0726813167551823</v>
+        <v>0.003272840157290791</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1.137475768462195</v>
+        <v>1.007836767559793</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1220563520675992</v>
+        <v>-0.1321147286483807</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.07113112995680071</v>
+        <v>0.1030849568548795</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1032486343009715</v>
+        <v>0.09660677267937112</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.0291117553610396</v>
+        <v>0.005907481457259278</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -3950,28 +3959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.0534149946425504</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.08126757478702552</v>
+        <v>0.2216991067360385</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962864</v>
+        <v>0.2389480542019929</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573141</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3980,10 +3989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.121721302370637</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3992,7 +4001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756414</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4038,49 +4047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.007859810079828833</v>
+        <v>0.1991773958883538</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.01519436250049544</v>
+        <v>0.1383712990484478</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.07584506561778721</v>
+        <v>0.2057028412243141</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2200814955608064</v>
+        <v>0.2187686648988483</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9636627906976745</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.4884434813691407</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.004612638980404427</v>
+        <v>0.03034451613625655</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9810109562715352</v>
+        <v>0.9700784615125182</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2469279583475472</v>
+        <v>1.344173815041704</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.01971605842128599</v>
+        <v>0.1048453029257503</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9078002770441739</v>
+        <v>1.198313531356619</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.03283823265868402</v>
+        <v>-0.1220563520675992</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4140,58 +4149,58 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.007859810079829055</v>
+        <v>-0.03588315428087374</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.01519436250049522</v>
+        <v>-0.08477015172327707</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.07584506561778712</v>
+        <v>0.08522082414153055</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2200814955608066</v>
+        <v>0.04852502486469504</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.08701691433111236</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.004612638980404427</v>
+        <v>0.8388723071338657</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9810109562715352</v>
+        <v>0.1728208842981709</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2469279583475474</v>
+        <v>0.05600734652469064</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.01971605842128576</v>
+        <v>-0.5022874374005696</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.9078002770441747</v>
+        <v>0.04992982339403304</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.03283823265868402</v>
+        <v>-0.01333427532540465</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.1960181629300093</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0</v>
+        <v>0.7847159647430844</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.5495183250710001</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4242,58 +4251,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.007859810079828833</v>
+        <v>0.219973425690712</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.01519436250049544</v>
+        <v>0.1581128348231637</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.07584506561778721</v>
+        <v>0.1716435077047097</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2200814955608064</v>
+        <v>0.1999916015372289</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9607558139534884</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.004612638980404427</v>
+        <v>0.1367261802868205</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.9810109562715352</v>
+        <v>0.8651796704442967</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2469279583475472</v>
+        <v>1.161639904847755</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.01971605842128599</v>
+        <v>0.01881425351789412</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9078002770441739</v>
+        <v>1.035586916636739</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.03283823265868402</v>
+        <v>-0.1172405796580748</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0</v>
+        <v>0.01734191277592623</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.1032486343009715</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.07786705449173448</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -4344,58 +4353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.12013798743183</v>
+        <v>0.4587322504434632</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1402642892068867</v>
+        <v>0.3847650335929069</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1941024876751377</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1069807703566161</v>
+        <v>0.0697761368206746</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.193060997030619</v>
+        <v>0.144427223143356</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9295058139534884</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1917257101080129</v>
+        <v>-0.2869026592132758</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.004612638980404649</v>
+        <v>0.4362751871824671</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.9810109562715347</v>
+        <v>0.5698061308410138</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1941024876751377</v>
+        <v>-0.2869026592132757</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.08856860050039383</v>
+        <v>1.045628509614295</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1442117315329907</v>
+        <v>-0.03586370776940528</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.3256115695028219</v>
+        <v>0.9321642616614942</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.0004382006475144307</v>
+        <v>-0.1220563520675992</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.1269996047382033</v>
+        <v>0.216444085291343</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.3939756699714687</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1269996047382034</v>
+        <v>-0.127356300762236</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -4446,58 +4455,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.0453726834078465</v>
+        <v>0.3039346135672543</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.06720919547678605</v>
+        <v>0.2378166441514451</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.08400699976983923</v>
+        <v>0.1630116906248304</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2070697545900752</v>
+        <v>0.2090293332448557</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9491279069767442</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.4425366612330849</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.004612638980404427</v>
+        <v>0.1228071056210567</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.9810109562715352</v>
+        <v>0.8789047246337144</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4425366612330848</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1810685166290817</v>
+        <v>1.339049983899392</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.07149206736049396</v>
+        <v>0.1024303622186051</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6656761375255211</v>
+        <v>1.19374570231434</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.02015338344400641</v>
+        <v>-0.1220563520675992</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.0528173590764166</v>
+        <v>0.08735756530942274</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.08973948813890953</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.0528173590764166</v>
+        <v>-0.002185772705690314</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4548,58 +4557,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.1201379874318304</v>
+        <v>0.3891351470281907</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.140264289206887</v>
+        <v>0.3186969561787549</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1941024876751383</v>
+        <v>-0.1710251013839396</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1069807703566164</v>
+        <v>0.07443483028736213</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1930609970306191</v>
+        <v>0.1254223907378349</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9338662790697675</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1917257101080133</v>
+        <v>-0.08701691433111214</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.004612638980403982</v>
+        <v>0.8388723071338662</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.981010956271537</v>
+        <v>0.1728208842981705</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1941024876751383</v>
+        <v>-0.1193545340586639</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.08856860050039406</v>
+        <v>0.5215343732359017</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1442117315329905</v>
+        <v>-0.2828773639893871</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.3256115695028227</v>
+        <v>0.4649411330013035</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0004382006475144307</v>
+        <v>-0.1220563520675991</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.1269996047382036</v>
+        <v>0.1584067142952739</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0.7847159647430848</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1269996047382032</v>
+        <v>-0.3509293707348946</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -4650,58 +4659,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.0453726834078465</v>
+        <v>0.2844762390765461</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.06720919547678605</v>
+        <v>0.2193449358601549</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.08400699976983923</v>
+        <v>0.1679147172827054</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2070697545900752</v>
+        <v>0.2069922632706336</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9498546511627907</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.004612638980404427</v>
+        <v>0.1367261802868205</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.9810109562715352</v>
+        <v>0.8651796704442967</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.435625969452745</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1810685166290817</v>
+        <v>1.275930800414455</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.07149206736049396</v>
+        <v>0.0726813167551823</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6656761375255211</v>
+        <v>1.137475768462195</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.02015338344400641</v>
+        <v>-0.1220563520675992</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.0528173590764166</v>
+        <v>0.07113112995680071</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>0.1032486343009715</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.0528173590764166</v>
+        <v>-0.0291117553610396</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4950,28 +4959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.01891210187562642</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570336</v>
+        <v>0.08099293800751969</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886579</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4980,10 +4989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4992,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.05185156587886031</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5038,49 +5047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.06404560575472296</v>
+        <v>0.005589722741125236</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.03077067932102873</v>
+        <v>-0.01307510148321644</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1160654159706605</v>
+        <v>0.07558961362210245</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4686838807519479</v>
+        <v>0.2193422573785161</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088221</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.02087621099141768</v>
+        <v>0.00677452384599353</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.051056249472068</v>
+        <v>0.9727270421740364</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.5310826913419402</v>
+        <v>0.2469279583475472</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.01010543144869347</v>
+        <v>-0.01971605842128599</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9714105862119542</v>
+        <v>0.9078002770441739</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.06450069847101803</v>
+        <v>-0.03283823265868402</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5140,49 +5149,49 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.06404560575472318</v>
+        <v>0.005589722741125458</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.0307706793210285</v>
+        <v>-0.01307510148321622</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751379</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1160654159706604</v>
+        <v>0.07558961362210237</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4686838807519483</v>
+        <v>0.2193422573785163</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088221</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.02087621099141768</v>
+        <v>0.00677452384599353</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.051056249472068</v>
+        <v>0.9727270421740364</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751379</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.5310826913419406</v>
+        <v>0.2469279583475474</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.01010543144869325</v>
+        <v>-0.01971605842128576</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.9714105862119551</v>
+        <v>0.9078002770441747</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.06450069847101803</v>
+        <v>-0.03283823265868402</v>
       </c>
       <c r="Y4" s="2" t="n">
         <v>2.220446049250313e-16</v>
@@ -5242,49 +5251,49 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.06404560575472296</v>
+        <v>0.005589722741125236</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.03077067932102873</v>
+        <v>-0.01307510148321644</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1160654159706605</v>
+        <v>0.07558961362210245</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4686838807519479</v>
+        <v>0.2193422573785161</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088221</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02087621099141768</v>
+        <v>0.00677452384599353</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.051056249472068</v>
+        <v>0.9727270421740364</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.5310826913419402</v>
+        <v>0.2469279583475472</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.01010543144869347</v>
+        <v>-0.01971605842128599</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9714105862119542</v>
+        <v>0.9078002770441739</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.06450069847101803</v>
+        <v>-0.03283823265868402</v>
       </c>
       <c r="Y5" s="2" t="n">
         <v>0</v>
@@ -5344,58 +5353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.06404560575472318</v>
+        <v>-0.1221197745757971</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.0307706793210285</v>
+        <v>-0.1384141735011394</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751377</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1160654159706604</v>
+        <v>0.1066183710672308</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4686838807519481</v>
+        <v>0.1924025640882426</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9931506849315068</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.193546254208822</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.02087621099141768</v>
+        <v>0.006774523845993752</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.051056249472068</v>
+        <v>0.9727270421740358</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751377</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.5310826913419404</v>
+        <v>0.08856860050039383</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.01010543144869336</v>
+        <v>-0.1442117315329907</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9714105862119546</v>
+        <v>0.3256115695028219</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.06450069847101803</v>
+        <v>-0.0004382006475144307</v>
       </c>
       <c r="Y6" s="2" t="n">
+        <v>-0.1269996047382034</v>
+      </c>
+      <c r="Z6" s="2" t="n">
         <v>2.220446049250313e-16</v>
       </c>
-      <c r="Z6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="AA6" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.1269996047382034</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -5446,58 +5455,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.06404560575472296</v>
+        <v>-0.04752287072844696</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.03077067932102873</v>
+        <v>-0.06520186822963336</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1160654159706605</v>
+        <v>0.08372345068901815</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4686838807519479</v>
+        <v>0.2063701390185318</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9931506849315068</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088221</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02087621099141768</v>
+        <v>0.00677452384599353</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.051056249472068</v>
+        <v>0.9727270421740364</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5310826913419402</v>
+        <v>0.1810685166290817</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.01010543144869347</v>
+        <v>-0.07149206736049396</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.9714105862119542</v>
+        <v>0.6656761375255211</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.06450069847101803</v>
+        <v>-0.02015338344400641</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0</v>
+        <v>-0.0528173590764166</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0</v>
+        <v>-0.0528173590764166</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5548,58 +5557,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.06404560575472207</v>
+        <v>-0.1221197745757975</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.03077067932102961</v>
+        <v>-0.1384141735011397</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.1941024876751383</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1160654159706604</v>
+        <v>0.1066183710672311</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4686838807519478</v>
+        <v>0.1924025640882427</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9931506849315068</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.1935462542088225</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02087621099141745</v>
+        <v>0.006774523845993086</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.051056249472067</v>
+        <v>0.9727270421740386</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3050371402068921</v>
+        <v>-0.1941024876751383</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.5310826913419389</v>
+        <v>0.08856860050039406</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.01010543144869436</v>
+        <v>-0.1442117315329905</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.9714105862119518</v>
+        <v>0.3256115695028227</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0645006984710178</v>
+        <v>-0.0004382006475144307</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>-0.1269996047382037</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-5.551115123125783e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>-0.1269996047382032</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -5650,58 +5659,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.06404560575472296</v>
+        <v>-0.04752287072844696</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.03077067932102873</v>
+        <v>-0.06520186822963336</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1160654159706605</v>
+        <v>0.08372345068901815</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4686838807519479</v>
+        <v>0.2063701390185318</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9931506849315068</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088221</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.02087621099141768</v>
+        <v>0.00677452384599353</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.051056249472068</v>
+        <v>0.9727270421740364</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.5310826913419402</v>
+        <v>0.1810685166290817</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.01010543144869347</v>
+        <v>-0.07149206736049396</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.9714105862119542</v>
+        <v>0.6656761375255211</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.06450069847101803</v>
+        <v>-0.02015338344400641</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0</v>
+        <v>-0.0528173590764166</v>
       </c>
       <c r="Z9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0</v>
+        <v>-0.0528173590764166</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5950,28 +5959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363057</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1799741913752893</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2405796270435321</v>
+        <v>0.4518304992174231</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450099</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5980,10 +5989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241682997</v>
+        <v>0.5657770181230004</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5992,7 +6001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174769</v>
+        <v>-0.05185156587886031</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6038,49 +6047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.07593530609125765</v>
+        <v>0.07322454526542055</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.1290764775225159</v>
+        <v>-0.0343123238727534</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.298221368786892</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1908003349426301</v>
+        <v>0.1142230623487696</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1967758842540266</v>
+        <v>0.4612108270599598</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.8968253968253969</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2809671323736413</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.04182193013870528</v>
+        <v>-0.02087621099141768</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9068390294167656</v>
+        <v>1.051056249472068</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2809671323736415</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2851494493697155</v>
+        <v>0.5442905043658335</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.164038021006592</v>
+        <v>-0.01372258853493979</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.530678422094654</v>
+        <v>0.9620230001062083</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1279869945573349</v>
+        <v>-0.06450069847101803</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6140,68 +6149,64 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.123185785230272</v>
+        <v>0.07322454526542055</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.05859354536273642</v>
+        <v>-0.0343123238727534</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.00942253736259735</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0006360007504951526</v>
+        <v>0.1142230623487695</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.02018470284987558</v>
+        <v>0.46121082705996</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.009746588693957114</v>
+        <v>0.8968253968253969</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>-0.02087621099141768</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>1.051056249472068</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1106314540976914</v>
+        <v>0.5442905043658339</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2775582102492622</v>
+        <v>-0.01372258853493957</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.2058910708906152</v>
+        <v>0.9620230001062091</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.00942253736259735</v>
+        <v>-0.06450069847101803</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.2154839294630535</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.4064778166545429</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1357958760030704</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="n">
-        <v>0.3125812952861471</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>-0.2377963300225924</v>
-      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6246,68 +6251,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.04318694445603577</v>
+        <v>0.07322454526542055</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.0168047169672535</v>
+        <v>-0.0343123238727534</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1240441358056347</v>
+        <v>0.1142230623487696</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1643136203906092</v>
+        <v>0.4612108270599598</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9805068226120858</v>
+        <v>0.8968253968253969</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1179533974995302</v>
+        <v>-0.02087621099141768</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7372514143129777</v>
+        <v>1.051056249472068</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.3520202466467532</v>
+        <v>0.5442905043658335</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1205400106732447</v>
+        <v>-0.01372258853493979</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.6551285631053725</v>
+        <v>0.9620230001062083</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.08922573857760219</v>
+        <v>-0.06450069847101803</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.1289111588534055</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.07307531657611488</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.05203347930455382</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.3125812952861471</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.08318174614964868</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6352,58 +6353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.1847525839528147</v>
+        <v>0.07322454526542055</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2316358844193643</v>
+        <v>-0.0343123238727534</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2830886953761897</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2146905675263885</v>
+        <v>0.1142230623487695</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1799452418984483</v>
+        <v>0.4612108270599599</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.8968253968253969</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2809671323736413</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.04182193013870528</v>
+        <v>-0.02087621099141768</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.9068390294167656</v>
+        <v>1.051056249472068</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2809671323736413</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1338110575368356</v>
+        <v>0.5442905043658337</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.2624803785054345</v>
+        <v>-0.01372258853493968</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.2490295563586896</v>
+        <v>0.9620230001062088</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.08538770826029607</v>
+        <v>-0.06450069847101803</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.117759371804658</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.117759371804658</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -6454,49 +6455,49 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.07593530609125765</v>
+        <v>0.07322454526542055</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1290764775225159</v>
+        <v>-0.0343123238727534</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.298221368786892</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1908003349426301</v>
+        <v>0.1142230623487696</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1967758842540266</v>
+        <v>0.4612108270599598</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.8968253968253969</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2809671323736413</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.04182193013870528</v>
+        <v>-0.02087621099141768</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.9068390294167656</v>
+        <v>1.051056249472068</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2809671323736415</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.2851494493697155</v>
+        <v>0.5442905043658335</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.164038021006592</v>
+        <v>-0.01372258853493979</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.530678422094654</v>
+        <v>0.9620230001062083</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1279869945573349</v>
+        <v>-0.06450069847101803</v>
       </c>
       <c r="Y7" s="2" t="n">
         <v>0</v>
@@ -6556,58 +6557,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.123185785230272</v>
+        <v>0.07322454526541944</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.05859354536273642</v>
+        <v>-0.0343123238727544</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.00942253736259735</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.0006360007504951526</v>
+        <v>0.1142230623487696</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0201847028498755</v>
+        <v>0.4612108270599597</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.009746588693957114</v>
+        <v>0.8968253968253969</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>-0.02087621099141745</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>1.051056249472067</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0</v>
+        <v>-0.3050371402068921</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1106314540976916</v>
+        <v>0.5442905043658319</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.2775582102492621</v>
+        <v>-0.01372258853494079</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.2058910708906156</v>
+        <v>0.9620230001062057</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.00942253736259735</v>
+        <v>-0.0645006984710178</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.2154839294630535</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.4064778166545429</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1357958760030703</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -6658,58 +6659,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.04318694445603577</v>
+        <v>0.07322454526542055</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.0168047169672535</v>
+        <v>-0.0343123238727534</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1240441358056347</v>
+        <v>0.1142230623487696</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1643136203906092</v>
+        <v>0.4612108270599598</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9805068226120858</v>
+        <v>0.8968253968253969</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1179533974995302</v>
+        <v>-0.02087621099141768</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7372514143129777</v>
+        <v>1.051056249472068</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.3520202466467532</v>
+        <v>0.5442905043658335</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1205400106732447</v>
+        <v>-0.01372258853493979</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6551285631053725</v>
+        <v>0.9620230001062083</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.08922573857760219</v>
+        <v>-0.06450069847101803</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1289111588534055</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.07307531657611488</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.05203347930455382</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -6958,28 +6959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003974677</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.103821015825279</v>
+        <v>0.1799741913752893</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213005</v>
+        <v>0.2405796270435321</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138072</v>
+        <v>-0.3098313187450099</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6988,10 +6989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922785</v>
+        <v>0.5373300241682997</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7000,7 +7001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174769</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7046,49 +7047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.002943983606027434</v>
+        <v>-0.07593530609125765</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.00535283614996529</v>
+        <v>-0.1290764775225159</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2112316646811809</v>
+        <v>-0.298221368786892</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.09716721907930907</v>
+        <v>0.1908003349426301</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.3134216093716399</v>
+        <v>0.1967758842540266</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9772727272727273</v>
+        <v>1</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2112316646811809</v>
+        <v>-0.2809671323736413</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.01671768863812972</v>
+        <v>0.04182193013870528</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9421521349130372</v>
+        <v>0.9068390294167656</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2112316646811809</v>
+        <v>-0.2809671323736415</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2715317523498695</v>
+        <v>0.2851494493697155</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.01117798245783186</v>
+        <v>-0.164038021006592</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9497252557220541</v>
+        <v>0.530678422094654</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.04769139338712791</v>
+        <v>-0.1279869945573349</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7148,67 +7149,67 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.123185785230272</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>0.05859354536273642</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>0.0006360007504951526</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.02018470284987558</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0</v>
+        <v>0.009746588693957114</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1106314540976914</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2775582102492622</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2058910708906152</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.01191759412390914</v>
+        <v>0.2154839294630535</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.2750259996931479</v>
+        <v>0.4064778166545429</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2063553257992853</v>
+        <v>-0.1357958760030704</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
-        <v>0.04615004380353627</v>
+        <v>0.3125812952861471</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>-0.03928937419683753</v>
+        <v>-0.2377963300225924</v>
       </c>
     </row>
     <row r="5">
@@ -7254,67 +7255,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>0.04318694445603577</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>-0.0168047169672535</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0.1240441358056347</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>0.1643136203906092</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.9805068226120858</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.1179533974995302</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>0.7372514143129777</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.3520202466467532</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.1205400106732447</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.6551285631053725</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>-0.08922573857760219</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.0622105130556192</v>
+        <v>0.1289111588534055</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.109227416058032</v>
+        <v>0.07307531657611488</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1545561592075562</v>
+        <v>0.05203347930455382</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.04615004380353627</v>
+        <v>0.3125812952861471</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.0214285775248475</v>
+        <v>-0.08318174614964868</v>
       </c>
     </row>
     <row r="6">
@@ -7360,68 +7361,64 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.1847525839528147</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>-0.2316358844193643</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>-0.2830886953761897</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>0.2146905675263885</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1799452418984483</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2809671323736413</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.04182193013870528</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.9068390294167656</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0</v>
+        <v>-0.2809671323736413</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1338110575368356</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2624803785054345</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2490295563586896</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0</v>
+        <v>-0.08538770826029607</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.01191759412390914</v>
+        <v>-0.117759371804658</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2750259996931479</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.2063553257992853</v>
+        <v>-0.117759371804658</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="n">
-        <v>0.04615004380353627</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.03928937419683753</v>
-      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7466,19 +7463,19 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>-0.07593530609125765</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>-0.1290764775225159</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.298221368786892</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0.1908003349426301</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>0.1967758842540266</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
@@ -7487,47 +7484,43 @@
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2809671323736413</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.04182193013870528</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>0.9068390294167656</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2809671323736415</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.2851494493697155</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.164038021006592</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.530678422094654</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>-0.1279869945573349</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.0622105130556192</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.109227416058032</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1545561592075562</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.04615004380353627</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>0.0214285775248475</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7572,68 +7565,64 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.123185785230272</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>0.05859354536273642</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0</v>
+        <v>0.0006360007504951526</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.0201847028498755</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0</v>
+        <v>0.009746588693957114</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1106314540976916</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2775582102492621</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2058910708906156</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0</v>
+        <v>-0.00942253736259735</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.01191759412390914</v>
+        <v>0.2154839294630535</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.2750259996931479</v>
+        <v>0.4064778166545429</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.2063553257992853</v>
+        <v>-0.1357958760030703</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="n">
-        <v>0.04615004380353627</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>-0.03928937419683753</v>
-      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7678,68 +7667,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>0.04318694445603577</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>-0.0168047169672535</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0.1240441358056347</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>0.1643136203906092</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.9805068226120858</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.1179533974995302</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>0.7372514143129777</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.3520202466467532</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.1205400106732447</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.6551285631053725</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>-0.08922573857760219</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.0622105130556192</v>
+        <v>0.1289111588534055</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.109227416058032</v>
+        <v>0.07307531657611488</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1545561592075562</v>
+        <v>0.05203347930455382</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.04615004380353627</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>0.0214285775248475</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7752,7 +7737,1031 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947871</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138072</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490124</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>0.002465108212122091</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.002447855702312429</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.2112316646811809</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.0966259064202601</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.31163690291174</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.9775280898876404</v>
+      </c>
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.2112316646811809</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.01671768863812972</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.9421521349130372</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.2112316646811809</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.2709246344263136</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.01885040907089353</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.9173239732170286</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.04769139338712791</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>0.01257069321498827</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.2750259996931479</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.2058431016632783</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.03928937419683753</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>-0.05663389030906907</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>-0.06125721696357767</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.06782602895282974</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.2170118542583445</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.1277711346285673</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0.5578762400716401</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.07822701090317752</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.1676123335559584</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.2648689094166217</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>-0.04964464462786422</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>-0.05895367134183171</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.109227416058032</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.1516200239600505</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>0.0214285775248475</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>0.01257069321498827</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.2750259996931479</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.2058431016632783</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.03928937419683753</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>-0.05663389030906907</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-0.06125721696357767</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.06782602895282974</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.2170118542583445</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.1277711346285673</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.5578762400716401</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.07822701090317752</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.1676123335559584</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.2648689094166217</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>-0.04964464462786422</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>-0.05895367134183171</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.109227416058032</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.1516200239600505</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>0.0214285775248475</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>0.01257069321498827</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.2750259996931479</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.2058431016632783</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.03928937419683753</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>-0.05663389030906907</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.06125721696357767</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.06782602895282974</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.2170118542583445</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.1277711346285673</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.5578762400716401</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.07822701090317752</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.1676123335559584</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.2648689094166217</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>-0.04964464462786422</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>-0.05895367134183171</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.109227416058032</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.1516200239600505</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.04615004380353627</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>0.0214285775248475</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7858,12 +8867,8 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>563</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -7872,10 +8877,10 @@
       </c>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.5562326869806095</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -7906,10 +8911,10 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>963</v>
+        <v>563</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -7919,7 +8924,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.9149709302325582</v>
+        <v>0.5568496949528563</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -7952,8 +8957,12 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>963</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -7962,10 +8971,10 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.9149709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8038,24 +9047,20 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-251</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>307</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -8086,21 +9091,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-251</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>307</v>
+      </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.9766081871345029</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -8117,30 +9124,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-30</v>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8170,15 +9179,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -8187,10 +9192,10 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="2" t="n">
-        <v>0.3655523255813953</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -8217,7 +9222,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
@@ -8226,16 +9231,14 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -8262,11 +9265,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -8275,10 +9282,10 @@
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>0.3655523255813953</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -8305,7 +9312,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
@@ -8317,13 +9324,13 @@
         <v>1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4873294346978557</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -8350,22 +9357,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-30</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -8385,37 +9390,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-193</v>
-      </c>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>57</v>
+      </c>
       <c r="J14" s="2" t="n">
-        <v>0.2770083102493075</v>
+        <v>0.4873294346978557</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -8432,37 +9435,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>209</v>
-      </c>
+        <v>-30</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.3670058139534884</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -8489,25 +9490,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-134</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -8534,11 +9537,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-193</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -8547,10 +9554,10 @@
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0</v>
+        <v>0.2773155851358846</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -8577,14 +9584,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8594,7 +9601,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.3670058139534884</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -8624,30 +9631,165 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-30</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>307</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
